--- a/excel-templates/Template_User_02_Assign.xlsx
+++ b/excel-templates/Template_User_02_Assign.xlsx
@@ -479,7 +479,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>User ID</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
